--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.48931705832253</v>
+        <v>9.829514021977412</v>
       </c>
       <c r="D2" t="n">
-        <v>55.62260746650349</v>
+        <v>9.038673713306817</v>
       </c>
       <c r="E2" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F2" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.82445876963843</v>
+        <v>8.583974550066245</v>
       </c>
       <c r="D3" t="n">
-        <v>52.89158415347961</v>
+        <v>8.594882424940437</v>
       </c>
       <c r="E3" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F3" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.06363647207299</v>
+        <v>9.272840926711861</v>
       </c>
       <c r="D4" t="n">
-        <v>56.29639323503442</v>
+        <v>9.148163900693092</v>
       </c>
       <c r="E4" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F4" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.07188386316454</v>
+        <v>8.136681127764238</v>
       </c>
       <c r="D5" t="n">
-        <v>49.44019072273282</v>
+        <v>8.034030992444084</v>
       </c>
       <c r="E5" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F5" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.52685791735998</v>
+        <v>6.260614411570997</v>
       </c>
       <c r="D6" t="n">
-        <v>28.62992677229135</v>
+        <v>4.652363100497344</v>
       </c>
       <c r="E6" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F6" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.11827046833403</v>
+        <v>9.11921895110428</v>
       </c>
       <c r="D7" t="n">
-        <v>54.80343559270531</v>
+        <v>8.905558283814612</v>
       </c>
       <c r="E7" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F7" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.87267389626396</v>
+        <v>6.966809508142894</v>
       </c>
       <c r="D8" t="n">
-        <v>41.69009827300002</v>
+        <v>6.774640969362503</v>
       </c>
       <c r="E8" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F8" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.95109631820736</v>
+        <v>7.954553151708697</v>
       </c>
       <c r="D9" t="n">
-        <v>47.58240028030013</v>
+        <v>7.732140045548771</v>
       </c>
       <c r="E9" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F9" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.19237195380507</v>
+        <v>6.206260442493324</v>
       </c>
       <c r="D10" t="n">
-        <v>36.81249988324273</v>
+        <v>5.982031231026943</v>
       </c>
       <c r="E10" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F10" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>70.08630473189392</v>
+        <v>11.38902451893276</v>
       </c>
       <c r="D11" t="n">
-        <v>68.55631189118475</v>
+        <v>11.14040068231752</v>
       </c>
       <c r="E11" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F11" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.27369640310395</v>
+        <v>4.269475665504392</v>
       </c>
       <c r="D12" t="n">
-        <v>24.83995462030338</v>
+        <v>4.036492625799299</v>
       </c>
       <c r="E12" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F12" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.20104975502176</v>
+        <v>2.957670585191036</v>
       </c>
       <c r="D13" t="n">
-        <v>18.30981590162713</v>
+        <v>2.975345084014409</v>
       </c>
       <c r="E13" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F13" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>69.88578842051967</v>
+        <v>11.35644061833445</v>
       </c>
       <c r="D14" t="n">
-        <v>68.39714860283429</v>
+        <v>11.11453664796057</v>
       </c>
       <c r="E14" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F14" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.06582910918145</v>
+        <v>4.885697230241986</v>
       </c>
       <c r="D15" t="n">
-        <v>29.58420441532571</v>
+        <v>4.807433217490428</v>
       </c>
       <c r="E15" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F15" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.18673277666391</v>
+        <v>6.205344076207886</v>
       </c>
       <c r="D16" t="n">
-        <v>37.46458290301292</v>
+        <v>6.0879947217396</v>
       </c>
       <c r="E16" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F16" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>50.23428815205866</v>
+        <v>8.163071824709533</v>
       </c>
       <c r="D17" t="n">
-        <v>49.20986170462917</v>
+        <v>7.99660252700224</v>
       </c>
       <c r="E17" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F17" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.07318161606818</v>
+        <v>7.974392012611079</v>
       </c>
       <c r="D18" t="n">
-        <v>6.169449964346442</v>
+        <v>1.002535619206297</v>
       </c>
       <c r="E18" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F18" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>58.79647010527722</v>
+        <v>9.554426392107548</v>
       </c>
       <c r="D19" t="n">
-        <v>12.95148873469552</v>
+        <v>2.104616919388021</v>
       </c>
       <c r="E19" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F19" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>78.64582766732798</v>
+        <v>12.7799469959408</v>
       </c>
       <c r="D20" t="n">
-        <v>36.1210663497129</v>
+        <v>5.869673281828347</v>
       </c>
       <c r="E20" t="n">
-        <v>15.08668964888778</v>
+        <v>2.451587067944264</v>
       </c>
       <c r="F20" t="n">
-        <v>17.14413301009373</v>
+        <v>2.785921614140231</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
